--- a/CSR_NAME.xlsx
+++ b/CSR_NAME.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="พนักงาน" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="พนักงาน" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,34 @@
           <t>โรคประจำตัว</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:20:48</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>หหหหหหหหหหหหหหหหหห</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ทรัพยากรมนุษย์</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0918848878</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CSR_NAME.xlsx
+++ b/CSR_NAME.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,34 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:21:05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ฟหกฟหกฟกหกฟ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ทรัพยากรมนุษย์</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>091884887</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CSR_NAME.xlsx
+++ b/CSR_NAME.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,38 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:53:28</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>แพตตี้</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ขายและการตลาด</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0983882219</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ไม่มี</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
